--- a/artfynd/A 52016-2019 artfynd.xlsx
+++ b/artfynd/A 52016-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 52016-2019 artfynd.xlsx
+++ b/artfynd/A 52016-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2241,6 +2241,317 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>114933421</v>
+      </c>
+      <c r="B15" t="n">
+        <v>90243</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Skalleråsen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>577322</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6625665</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Haraker</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-11-02</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-11-04</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anders Esplund, Sofia Berg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>114933414</v>
+      </c>
+      <c r="B16" t="n">
+        <v>5162</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Skalleråsen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>577351</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6625870</v>
+      </c>
+      <c r="S16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Haraker</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-11-02</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-11-04</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Gamla gnagspår</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anders Esplund, Sofia Berg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>114933413</v>
+      </c>
+      <c r="B17" t="n">
+        <v>90207</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Skalleråsen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>577352</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6625874</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Haraker</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-11-02</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-11-04</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anders Esplund, Sofia Berg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
